--- a/excel-files/VALENZUELA/ANDRES FERNANDO ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/VALENZUELA/ANDRES FERNANDO ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CF87705-58C9-4755-9464-090035981BBC}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30349135-F303-48CF-93EC-AD4FB1E117E9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -736,6 +736,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -747,12 +753,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:8" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="19.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="19.5">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -5338,11 +5338,11 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E61:E69 E51:E59 E71:E79 E81:E89 E91:E98" xr:uid="{E8BCD515-11AF-4194-AB2A-AF16DCCBFEC4}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5384,38 +5384,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5454,10 +5454,10 @@
       <c r="L2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>46</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5490,10 +5490,10 @@
       <c r="X2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>58</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -5511,7 +5511,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="34"/>
-      <c r="F3" s="32"/>
+      <c r="F3" s="1"/>
       <c r="G3" s="34"/>
       <c r="H3" s="34">
         <f>IF((D3-E3)&lt;0,0,(D3-E3))</f>
@@ -5526,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="34"/>
-      <c r="L3" s="32"/>
+      <c r="L3" s="1"/>
       <c r="M3" s="34"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3" si="0">IF((J3-K3)&lt;0,0,(J3-K3))</f>
@@ -5541,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="34"/>
-      <c r="R3" s="32"/>
+      <c r="R3" s="1"/>
       <c r="S3" s="34"/>
       <c r="T3" s="34">
         <f>IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="W3" s="34"/>
-      <c r="X3" s="32"/>
+      <c r="X3" s="1"/>
       <c r="Y3" s="34"/>
       <c r="Z3" s="34">
         <f>IF((V3-W3)&lt;0,0,(V3-W3))</f>
@@ -5579,7 +5579,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6144,7 +6144,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6489,7 +6489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6710,7 +6710,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7345,7 +7345,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7621,7 +7621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7690,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -7980,7 +7980,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8615,7 +8615,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -8960,7 +8960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9098,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9167,7 +9167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9250,7 +9250,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9885,7 +9885,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10299,7 +10299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10520,7 +10520,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10727,7 +10727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10796,7 +10796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10865,7 +10865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11003,7 +11003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11155,7 +11155,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11293,7 +11293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11431,7 +11431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11500,7 +11500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11707,7 +11707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11790,7 +11790,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -11859,7 +11859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -11997,7 +11997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12135,7 +12135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12273,7 +12273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -13525,7 +13525,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="H5:K5 H33:I41 H43:I51 H53:I61 H63:I71 H73:I81 H83:I91 H93:I101 H103:I110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:K12 K112:L127 Q112:R126 P2:R2 N13:P126 T13:V127 J6:J127 N4:P4 T4:V4 J4 Z4:AA127 Y13 D2:F3 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 J2:L3 L5:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 N3:R3 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 V2:X3 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W63:X71 W73:X81 W83:X91 W93:X101 W103:X110" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13535,15 +13535,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 R112:R127 L112:L127 F112:F127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F3 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 L5:L12 L3 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 R5:R12 R3 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 X5:X12 X3 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{08145D80-1E47-4848-88D9-A18FA452871F}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13588,38 +13591,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13658,10 +13661,10 @@
       <c r="L2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>72</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -13694,10 +13697,10 @@
       <c r="X2" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -13773,7 +13776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13842,7 +13845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13911,7 +13914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -13980,7 +13983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14049,7 +14052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14118,7 +14121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14187,7 +14190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14257,7 +14260,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14326,7 +14329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14395,7 +14398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14464,7 +14467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14533,7 +14536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14602,7 +14605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14671,7 +14674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14740,7 +14743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14810,7 +14813,7 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14879,7 +14882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -14948,7 +14951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15017,7 +15020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15086,7 +15089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15155,7 +15158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15224,7 +15227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15293,7 +15296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15362,7 +15365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15432,7 +15435,7 @@
       </c>
     </row>
     <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15501,7 +15504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15570,7 +15573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15639,7 +15642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15708,7 +15711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15777,7 +15780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15846,7 +15849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -15915,7 +15918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -15984,7 +15987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16053,7 +16056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16122,7 +16125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16191,8 +16194,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16261,7 +16264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16330,7 +16333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16399,7 +16402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16468,7 +16471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16537,7 +16540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16606,7 +16609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16675,7 +16678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16744,7 +16747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16813,7 +16816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16882,7 +16885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -16951,8 +16954,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17021,7 +17024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17090,7 +17093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17159,7 +17162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17228,7 +17231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17297,7 +17300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17366,7 +17369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17435,7 +17438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17504,7 +17507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17573,7 +17576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17642,7 +17645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17711,8 +17714,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17781,7 +17784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17850,7 +17853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -17919,7 +17922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -17988,7 +17991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18057,7 +18060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18126,7 +18129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18195,7 +18198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18264,7 +18267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18333,7 +18336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18402,7 +18405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18471,8 +18474,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18541,7 +18544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18610,7 +18613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18679,7 +18682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18748,7 +18751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18817,7 +18820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -18886,7 +18889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -18955,7 +18958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19024,7 +19027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19093,7 +19096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19162,7 +19165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19232,7 +19235,7 @@
       </c>
     </row>
     <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19301,7 +19304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19370,7 +19373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19439,7 +19442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19508,7 +19511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19577,7 +19580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19646,7 +19649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19715,7 +19718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19784,7 +19787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19853,7 +19856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -19922,7 +19925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -19991,8 +19994,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20061,7 +20064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20130,7 +20133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20199,7 +20202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20268,7 +20271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20337,7 +20340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20406,7 +20409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20475,7 +20478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20544,7 +20547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20613,7 +20616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20682,7 +20685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20751,8 +20754,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="114" spans="1:28" s="7" customFormat="1" ht="15"/>
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
       </c>
@@ -20821,7 +20824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -20890,7 +20893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -20959,7 +20962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21028,7 +21031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21097,7 +21100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21166,7 +21169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21235,7 +21238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21998,7 +22001,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 P2:R2 V2:X2 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D103:F113 D115:F122 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89 H91:L101 H103:L113 H115:L122 N3:R10 N12:R19 N21:R29 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 N115:R122 T3:X10 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65 T67:X77 T79:X89 T91:X101 T103:X113 T115:X122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22012,8 +22015,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 X115:X122" xr:uid="{48291EDD-C6F3-42DC-AF34-D412423A4601}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
